--- a/data/software.xlsx
+++ b/data/software.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="438">
   <si>
     <t>tool_name</t>
   </si>
@@ -633,6 +633,33 @@
     <t>https://github.com/UofUEpiBio/epiworldpy</t>
   </si>
   <si>
+    <t>epiworldRcalibrate: Fast and Effortless Calibration of Agent-Based Models using Machine Learning</t>
+  </si>
+  <si>
+    <t>Provides tools and pre-trained Machine Learning [ML] models for calibration of Agent-Based Models [ABMs] built with the R package 'epiworldR'. Implements methods described in Najafzadehkhoei, Vega Yon, Modenesi, and Meyer (2025) &lt;doi:10.48550/arXiv.2509.07013&gt;. Users can automatically calibrate ABMs in seconds with pre-trained ML models, effectively focusing on simulation rather than calibration. Bridges a gap by allowing public health practitioners to run their own ABMs without the advanced technical expertise often required by calibration.</t>
+  </si>
+  <si>
+    <t>Sima Najafzadehkhoei</t>
+  </si>
+  <si>
+    <t>sima.njf@utah.edu</t>
+  </si>
+  <si>
+    <t>Parameter estimation</t>
+  </si>
+  <si>
+    <t>Observed incidence data and model parameters to calibrate</t>
+  </si>
+  <si>
+    <t>https://sima-njf.github.io/epiworldRcalibrate/, https://github.com/sima-njf/epiworldRcalibrate</t>
+  </si>
+  <si>
+    <t>https://github.com/sima-njf/epiworldRcalibrate</t>
+  </si>
+  <si>
+    <t>epiworldRcalibrate</t>
+  </si>
+  <si>
     <t>Excess Death Estimation</t>
   </si>
   <si>
@@ -1166,10 +1193,10 @@
     <t>Public health professionals, dashboard and report builders</t>
   </si>
   <si>
-    <t>https://epiforesite.github.io/branding-package/</t>
-  </si>
-  <si>
-    <t>https://github.com/EpiForeSITE/branding-package</t>
+    <t>https://epiforesite.github.io/rbranding/</t>
+  </si>
+  <si>
+    <t>https://github.com/EpiForeSITE/rbranding</t>
   </si>
   <si>
     <t>Room contamination simulator</t>
@@ -1653,7 +1680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P63"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1">
@@ -2794,136 +2821,145 @@
         <v>204</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>205</v>
       </c>
       <c r="D26" t="s">
-        <v>129</v>
+        <v>206</v>
       </c>
       <c r="E26" t="s">
         <v>43</v>
       </c>
-      <c r="F26" t="s">
-        <v>205</v>
-      </c>
       <c r="G26" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="H26" t="s">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="I26" t="s">
         <v>24</v>
       </c>
       <c r="J26" t="s">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="K26" t="s">
         <v>23</v>
       </c>
       <c r="L26" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="M26" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N26" t="s">
-        <v>208</v>
+        <v>209</v>
+      </c>
+      <c r="O26" t="s">
+        <v>210</v>
+      </c>
+      <c r="P26" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="27" spans="1:16">
       <c r="A27" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C27" t="s">
-        <v>211</v>
+        <v>128</v>
       </c>
       <c r="D27" t="s">
-        <v>212</v>
+        <v>129</v>
       </c>
       <c r="E27" t="s">
         <v>43</v>
       </c>
+      <c r="F27" t="s">
+        <v>214</v>
+      </c>
       <c r="G27" t="s">
-        <v>213</v>
+        <v>215</v>
+      </c>
+      <c r="H27" t="s">
+        <v>23</v>
       </c>
       <c r="I27" t="s">
         <v>24</v>
       </c>
+      <c r="J27" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>153</v>
+      </c>
+      <c r="M27" t="s">
+        <v>216</v>
+      </c>
       <c r="N27" t="s">
-        <v>214</v>
-      </c>
-      <c r="O27" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:16">
       <c r="A28" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B28" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C28" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D28" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E28" t="s">
         <v>43</v>
       </c>
-      <c r="F28" t="s">
-        <v>220</v>
-      </c>
       <c r="G28" t="s">
-        <v>221</v>
-      </c>
-      <c r="H28" t="s">
-        <v>23</v>
+        <v>222</v>
       </c>
       <c r="I28" t="s">
-        <v>222</v>
-      </c>
-      <c r="J28" t="s">
-        <v>23</v>
-      </c>
-      <c r="K28" t="s">
-        <v>23</v>
-      </c>
-      <c r="L28" t="s">
-        <v>25</v>
+        <v>24</v>
+      </c>
+      <c r="N28" t="s">
+        <v>223</v>
+      </c>
+      <c r="O28" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:16">
       <c r="A29" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B29" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>227</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>228</v>
       </c>
       <c r="E29" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="F29" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="G29" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="H29" t="s">
         <v>23</v>
       </c>
       <c r="I29" t="s">
-        <v>23</v>
+        <v>231</v>
       </c>
       <c r="J29" t="s">
         <v>23</v>
@@ -2932,42 +2968,36 @@
         <v>23</v>
       </c>
       <c r="L29" t="s">
-        <v>65</v>
-      </c>
-      <c r="M29" t="s">
-        <v>227</v>
-      </c>
-      <c r="N29" t="s">
-        <v>228</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:16">
       <c r="A30" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B30" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C30" t="s">
-        <v>18</v>
+        <v>137</v>
       </c>
       <c r="D30" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="E30" t="s">
         <v>20</v>
       </c>
       <c r="F30" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G30" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="H30" t="s">
         <v>23</v>
       </c>
       <c r="I30" t="s">
-        <v>233</v>
+        <v>23</v>
       </c>
       <c r="J30" t="s">
         <v>23</v>
@@ -2976,21 +3006,21 @@
         <v>23</v>
       </c>
       <c r="L30" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="M30" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="N30" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31" spans="1:16">
       <c r="A31" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B31" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
@@ -3002,16 +3032,16 @@
         <v>20</v>
       </c>
       <c r="F31" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="G31" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H31" t="s">
         <v>23</v>
       </c>
       <c r="I31" t="s">
-        <v>24</v>
+        <v>242</v>
       </c>
       <c r="J31" t="s">
         <v>23</v>
@@ -3020,42 +3050,42 @@
         <v>23</v>
       </c>
       <c r="L31" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="M31" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="N31" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="32" spans="1:16">
       <c r="A32" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B32" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C32" t="s">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>138</v>
+        <v>19</v>
       </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F32" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G32" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="H32" t="s">
         <v>23</v>
       </c>
       <c r="I32" t="s">
-        <v>246</v>
+        <v>24</v>
       </c>
       <c r="J32" t="s">
         <v>23</v>
@@ -3064,21 +3094,21 @@
         <v>23</v>
       </c>
       <c r="L32" t="s">
-        <v>247</v>
+        <v>65</v>
       </c>
       <c r="M32" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N32" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="33" spans="1:16">
       <c r="A33" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B33" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C33" t="s">
         <v>137</v>
@@ -3087,19 +3117,19 @@
         <v>138</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F33" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G33" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H33" t="s">
         <v>23</v>
       </c>
       <c r="I33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="J33" t="s">
         <v>23</v>
@@ -3108,42 +3138,42 @@
         <v>23</v>
       </c>
       <c r="L33" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="M33" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="N33" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" spans="1:16">
       <c r="A34" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B34" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C34" t="s">
-        <v>18</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>138</v>
       </c>
       <c r="E34" t="s">
         <v>20</v>
       </c>
       <c r="F34" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="G34" t="s">
-        <v>178</v>
+        <v>262</v>
       </c>
       <c r="H34" t="s">
         <v>23</v>
       </c>
       <c r="I34" t="s">
-        <v>24</v>
+        <v>263</v>
       </c>
       <c r="J34" t="s">
         <v>23</v>
@@ -3152,21 +3182,21 @@
         <v>23</v>
       </c>
       <c r="L34" t="s">
-        <v>65</v>
+        <v>256</v>
       </c>
       <c r="M34" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="N34" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B35" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C35" t="s">
         <v>18</v>
@@ -3178,10 +3208,10 @@
         <v>20</v>
       </c>
       <c r="F35" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G35" t="s">
-        <v>265</v>
+        <v>178</v>
       </c>
       <c r="H35" t="s">
         <v>23</v>
@@ -3196,42 +3226,42 @@
         <v>23</v>
       </c>
       <c r="L35" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="M35" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="N35" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36" spans="1:16">
       <c r="A36" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B36" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C36" t="s">
-        <v>270</v>
+        <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>271</v>
+        <v>19</v>
       </c>
       <c r="E36" t="s">
         <v>20</v>
       </c>
       <c r="F36" t="s">
-        <v>109</v>
+        <v>273</v>
       </c>
       <c r="G36" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H36" t="s">
         <v>23</v>
       </c>
       <c r="I36" t="s">
-        <v>273</v>
+        <v>24</v>
       </c>
       <c r="J36" t="s">
         <v>23</v>
@@ -3240,42 +3270,42 @@
         <v>23</v>
       </c>
       <c r="L36" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
       <c r="M36" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N36" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:16">
       <c r="A37" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B37" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>279</v>
       </c>
       <c r="D37" t="s">
-        <v>19</v>
+        <v>280</v>
       </c>
       <c r="E37" t="s">
         <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>278</v>
+        <v>109</v>
       </c>
       <c r="G37" t="s">
-        <v>22</v>
+        <v>281</v>
       </c>
       <c r="H37" t="s">
         <v>23</v>
       </c>
       <c r="I37" t="s">
-        <v>24</v>
+        <v>282</v>
       </c>
       <c r="J37" t="s">
         <v>23</v>
@@ -3284,130 +3314,130 @@
         <v>23</v>
       </c>
       <c r="L37" t="s">
-        <v>25</v>
+        <v>153</v>
       </c>
       <c r="M37" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="N37" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" spans="1:16">
       <c r="A38" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B38" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C38" t="s">
-        <v>283</v>
+        <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>284</v>
+        <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>43</v>
+        <v>20</v>
+      </c>
+      <c r="F38" t="s">
+        <v>287</v>
       </c>
       <c r="G38" t="s">
-        <v>285</v>
+        <v>22</v>
       </c>
       <c r="H38" t="s">
-        <v>179</v>
+        <v>23</v>
       </c>
       <c r="I38" t="s">
         <v>24</v>
       </c>
       <c r="J38" t="s">
-        <v>286</v>
+        <v>23</v>
       </c>
       <c r="K38" t="s">
-        <v>287</v>
+        <v>23</v>
       </c>
       <c r="L38" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38" t="s">
         <v>288</v>
       </c>
       <c r="N38" t="s">
         <v>289</v>
       </c>
-      <c r="O38" t="s">
-        <v>290</v>
-      </c>
     </row>
     <row r="39" spans="1:16">
       <c r="A39" t="s">
+        <v>290</v>
+      </c>
+      <c r="B39" t="s">
         <v>291</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>292</v>
       </c>
-      <c r="C39" t="s">
-        <v>18</v>
-      </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>293</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
-      </c>
-      <c r="F39" t="s">
-        <v>293</v>
+        <v>43</v>
       </c>
       <c r="G39" t="s">
-        <v>72</v>
+        <v>294</v>
       </c>
       <c r="H39" t="s">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="I39" t="s">
         <v>24</v>
       </c>
       <c r="J39" t="s">
-        <v>23</v>
+        <v>295</v>
       </c>
       <c r="K39" t="s">
-        <v>23</v>
+        <v>296</v>
       </c>
       <c r="L39" t="s">
-        <v>25</v>
-      </c>
-      <c r="M39" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="N39" t="s">
-        <v>295</v>
+        <v>298</v>
+      </c>
+      <c r="O39" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:16">
       <c r="A40" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B40" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="C40" t="s">
-        <v>185</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="E40" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F40" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G40" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="H40" t="s">
-        <v>179</v>
+        <v>23</v>
       </c>
       <c r="I40" t="s">
-        <v>299</v>
+        <v>24</v>
       </c>
       <c r="J40" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="K40" t="s">
         <v>23</v>
@@ -3416,136 +3446,133 @@
         <v>25</v>
       </c>
       <c r="M40" t="s">
-        <v>188</v>
+        <v>303</v>
       </c>
       <c r="N40" t="s">
-        <v>300</v>
-      </c>
-      <c r="O40" t="s">
-        <v>301</v>
-      </c>
-      <c r="P40" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B41" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C41" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="D41" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="E41" t="s">
         <v>43</v>
       </c>
       <c r="F41" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G41" t="s">
-        <v>306</v>
+        <v>178</v>
       </c>
       <c r="H41" t="s">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="I41" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J41" t="s">
-        <v>308</v>
+        <v>187</v>
       </c>
       <c r="K41" t="s">
         <v>23</v>
       </c>
       <c r="L41" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="M41" t="s">
+        <v>188</v>
+      </c>
+      <c r="N41" t="s">
         <v>309</v>
       </c>
-      <c r="N41" t="s">
+      <c r="O41" t="s">
         <v>310</v>
+      </c>
+      <c r="P41" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:16">
       <c r="A42" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B42" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
-        <v>313</v>
+        <v>138</v>
       </c>
       <c r="E42" t="s">
         <v>43</v>
       </c>
+      <c r="F42" t="s">
+        <v>314</v>
+      </c>
       <c r="G42" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H42" t="s">
-        <v>179</v>
+        <v>23</v>
       </c>
       <c r="I42" t="s">
-        <v>24</v>
+        <v>316</v>
       </c>
       <c r="J42" t="s">
-        <v>187</v>
+        <v>317</v>
       </c>
       <c r="K42" t="s">
         <v>23</v>
       </c>
       <c r="L42" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="M42" t="s">
-        <v>188</v>
+        <v>318</v>
       </c>
       <c r="N42" t="s">
-        <v>315</v>
-      </c>
-      <c r="O42" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="43" spans="1:16">
       <c r="A43" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="B43" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="C43" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>42</v>
+        <v>322</v>
       </c>
       <c r="E43" t="s">
         <v>43</v>
       </c>
-      <c r="F43" t="s">
-        <v>318</v>
-      </c>
       <c r="G43" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="H43" t="s">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="I43" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J43" t="s">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="K43" t="s">
         <v>23</v>
@@ -3554,42 +3581,42 @@
         <v>25</v>
       </c>
       <c r="M43" t="s">
-        <v>320</v>
+        <v>188</v>
       </c>
       <c r="N43" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="O43" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="44" spans="1:16">
       <c r="A44" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B44" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C44" t="s">
-        <v>270</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>271</v>
+        <v>42</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="F44" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G44" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="H44" t="s">
         <v>23</v>
       </c>
       <c r="I44" t="s">
-        <v>273</v>
+        <v>35</v>
       </c>
       <c r="J44" t="s">
         <v>23</v>
@@ -3601,39 +3628,42 @@
         <v>25</v>
       </c>
       <c r="M44" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N44" t="s">
-        <v>328</v>
+        <v>330</v>
+      </c>
+      <c r="O44" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="45" spans="1:16">
       <c r="A45" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B45" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>279</v>
       </c>
       <c r="D45" t="s">
-        <v>52</v>
+        <v>280</v>
       </c>
       <c r="E45" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F45" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G45" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="H45" t="s">
         <v>23</v>
       </c>
       <c r="I45" t="s">
-        <v>23</v>
+        <v>282</v>
       </c>
       <c r="J45" t="s">
         <v>23</v>
@@ -3642,42 +3672,42 @@
         <v>23</v>
       </c>
       <c r="L45" t="s">
-        <v>333</v>
+        <v>25</v>
       </c>
       <c r="M45" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N45" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="46" spans="1:16">
       <c r="A46" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B46" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C46" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="D46" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E46" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F46" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G46" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H46" t="s">
         <v>23</v>
       </c>
       <c r="I46" t="s">
-        <v>340</v>
+        <v>23</v>
       </c>
       <c r="J46" t="s">
         <v>23</v>
@@ -3686,45 +3716,42 @@
         <v>23</v>
       </c>
       <c r="L46" t="s">
-        <v>25</v>
+        <v>342</v>
       </c>
       <c r="M46" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N46" t="s">
-        <v>342</v>
-      </c>
-      <c r="O46" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="47" spans="1:16">
       <c r="A47" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B47" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C47" t="s">
-        <v>137</v>
+        <v>41</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="E47" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F47" t="s">
-        <v>53</v>
+        <v>347</v>
       </c>
       <c r="G47" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H47" t="s">
         <v>23</v>
       </c>
       <c r="I47" t="s">
-        <v>24</v>
+        <v>349</v>
       </c>
       <c r="J47" t="s">
         <v>23</v>
@@ -3736,36 +3763,36 @@
         <v>25</v>
       </c>
       <c r="M47" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N47" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="O47" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="48" spans="1:16">
       <c r="A48" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C48" t="s">
-        <v>352</v>
+        <v>137</v>
       </c>
       <c r="D48" t="s">
-        <v>353</v>
+        <v>138</v>
       </c>
       <c r="E48" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F48" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="G48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H48" t="s">
         <v>23</v>
@@ -3780,36 +3807,39 @@
         <v>23</v>
       </c>
       <c r="L48" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="M48" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N48" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15">
+        <v>357</v>
+      </c>
+      <c r="O48" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
       <c r="A49" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B49" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C49" t="s">
-        <v>115</v>
+        <v>361</v>
       </c>
       <c r="D49" t="s">
-        <v>108</v>
+        <v>362</v>
       </c>
       <c r="E49" t="s">
         <v>20</v>
       </c>
       <c r="F49" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="G49" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="H49" t="s">
         <v>23</v>
@@ -3818,232 +3848,235 @@
         <v>24</v>
       </c>
       <c r="J49" t="s">
-        <v>360</v>
+        <v>23</v>
       </c>
       <c r="K49" t="s">
         <v>23</v>
       </c>
       <c r="L49" t="s">
+        <v>65</v>
+      </c>
+      <c r="M49" t="s">
+        <v>364</v>
+      </c>
+      <c r="N49" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" t="s">
+        <v>366</v>
+      </c>
+      <c r="B50" t="s">
+        <v>367</v>
+      </c>
+      <c r="C50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D50" t="s">
+        <v>108</v>
+      </c>
+      <c r="E50" t="s">
+        <v>20</v>
+      </c>
+      <c r="F50" t="s">
+        <v>109</v>
+      </c>
+      <c r="G50" t="s">
+        <v>368</v>
+      </c>
+      <c r="H50" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" t="s">
+        <v>24</v>
+      </c>
+      <c r="J50" t="s">
+        <v>369</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
         <v>25</v>
       </c>
-      <c r="M49" t="s">
+      <c r="M50" t="s">
+        <v>370</v>
+      </c>
+      <c r="N50" t="s">
+        <v>371</v>
+      </c>
+      <c r="O50" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" t="s">
+        <v>372</v>
+      </c>
+      <c r="B51" t="s">
+        <v>373</v>
+      </c>
+      <c r="C51" t="s">
+        <v>374</v>
+      </c>
+      <c r="E51" t="s">
+        <v>43</v>
+      </c>
+      <c r="G51" t="s">
+        <v>178</v>
+      </c>
+      <c r="I51" t="s">
+        <v>35</v>
+      </c>
+      <c r="J51" t="s">
+        <v>187</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="N51" t="s">
+        <v>375</v>
+      </c>
+      <c r="O51" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52" t="s">
+        <v>377</v>
+      </c>
+      <c r="B52" t="s">
+        <v>378</v>
+      </c>
+      <c r="C52" t="s">
         <v>361</v>
       </c>
-      <c r="N49" t="s">
+      <c r="D52" t="s">
         <v>362</v>
-      </c>
-      <c r="O49" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15">
-      <c r="A50" t="s">
-        <v>363</v>
-      </c>
-      <c r="B50" t="s">
-        <v>364</v>
-      </c>
-      <c r="C50" t="s">
-        <v>365</v>
-      </c>
-      <c r="E50" t="s">
-        <v>43</v>
-      </c>
-      <c r="G50" t="s">
-        <v>178</v>
-      </c>
-      <c r="I50" t="s">
-        <v>35</v>
-      </c>
-      <c r="J50" t="s">
-        <v>187</v>
-      </c>
-      <c r="K50" t="s">
-        <v>23</v>
-      </c>
-      <c r="N50" t="s">
-        <v>366</v>
-      </c>
-      <c r="O50" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15">
-      <c r="A51" t="s">
-        <v>368</v>
-      </c>
-      <c r="B51" t="s">
-        <v>369</v>
-      </c>
-      <c r="C51" t="s">
-        <v>352</v>
-      </c>
-      <c r="D51" t="s">
-        <v>353</v>
-      </c>
-      <c r="E51" t="s">
-        <v>20</v>
-      </c>
-      <c r="F51" t="s">
-        <v>53</v>
-      </c>
-      <c r="G51" t="s">
-        <v>370</v>
-      </c>
-      <c r="H51" t="s">
-        <v>23</v>
-      </c>
-      <c r="I51" t="s">
-        <v>24</v>
-      </c>
-      <c r="J51" t="s">
-        <v>23</v>
-      </c>
-      <c r="K51" t="s">
-        <v>23</v>
-      </c>
-      <c r="L51" t="s">
-        <v>65</v>
-      </c>
-      <c r="N51" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15">
-      <c r="A52" t="s">
-        <v>372</v>
-      </c>
-      <c r="B52" t="s">
-        <v>373</v>
-      </c>
-      <c r="C52" t="s">
-        <v>84</v>
-      </c>
-      <c r="D52" t="s">
-        <v>85</v>
       </c>
       <c r="E52" t="s">
         <v>20</v>
       </c>
       <c r="F52" t="s">
-        <v>374</v>
+        <v>53</v>
       </c>
       <c r="G52" t="s">
+        <v>379</v>
+      </c>
+      <c r="H52" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" t="s">
+        <v>24</v>
+      </c>
+      <c r="J52" t="s">
+        <v>23</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>65</v>
+      </c>
+      <c r="N52" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" t="s">
+        <v>381</v>
+      </c>
+      <c r="B53" t="s">
+        <v>382</v>
+      </c>
+      <c r="C53" t="s">
+        <v>84</v>
+      </c>
+      <c r="D53" t="s">
+        <v>85</v>
+      </c>
+      <c r="E53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" t="s">
+        <v>383</v>
+      </c>
+      <c r="G53" t="s">
         <v>101</v>
       </c>
-      <c r="H52" t="s">
-        <v>23</v>
-      </c>
-      <c r="I52" t="s">
+      <c r="H53" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" t="s">
         <v>35</v>
       </c>
-      <c r="J52" t="s">
-        <v>23</v>
-      </c>
-      <c r="K52" t="s">
-        <v>23</v>
-      </c>
-      <c r="L52" t="s">
+      <c r="J53" t="s">
+        <v>23</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
         <v>25</v>
       </c>
-      <c r="M52" t="s">
-        <v>375</v>
-      </c>
-      <c r="N52" t="s">
+      <c r="M53" t="s">
+        <v>384</v>
+      </c>
+      <c r="N53" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:15">
-      <c r="A53" t="s">
-        <v>376</v>
-      </c>
-      <c r="B53" t="s">
-        <v>377</v>
-      </c>
-      <c r="C53" t="s">
-        <v>218</v>
-      </c>
-      <c r="D53" t="s">
-        <v>378</v>
-      </c>
-      <c r="E53" t="s">
+    <row r="54" spans="1:16">
+      <c r="A54" t="s">
+        <v>385</v>
+      </c>
+      <c r="B54" t="s">
+        <v>386</v>
+      </c>
+      <c r="C54" t="s">
+        <v>227</v>
+      </c>
+      <c r="D54" t="s">
+        <v>387</v>
+      </c>
+      <c r="E54" t="s">
         <v>43</v>
       </c>
-      <c r="G53" t="s">
-        <v>314</v>
-      </c>
-      <c r="H53" t="s">
+      <c r="G54" t="s">
+        <v>323</v>
+      </c>
+      <c r="H54" t="s">
         <v>179</v>
-      </c>
-      <c r="I53" t="s">
-        <v>24</v>
-      </c>
-      <c r="J53" t="s">
-        <v>379</v>
-      </c>
-      <c r="K53" t="s">
-        <v>23</v>
-      </c>
-      <c r="L53" t="s">
-        <v>288</v>
-      </c>
-      <c r="N53" t="s">
-        <v>380</v>
-      </c>
-      <c r="O53" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15">
-      <c r="A54" t="s">
-        <v>382</v>
-      </c>
-      <c r="B54" t="s">
-        <v>383</v>
-      </c>
-      <c r="C54" t="s">
-        <v>18</v>
-      </c>
-      <c r="D54" t="s">
-        <v>19</v>
-      </c>
-      <c r="E54" t="s">
-        <v>20</v>
-      </c>
-      <c r="F54" t="s">
-        <v>384</v>
-      </c>
-      <c r="G54" t="s">
-        <v>385</v>
-      </c>
-      <c r="H54" t="s">
-        <v>23</v>
       </c>
       <c r="I54" t="s">
         <v>24</v>
       </c>
       <c r="J54" t="s">
-        <v>23</v>
+        <v>388</v>
       </c>
       <c r="K54" t="s">
         <v>23</v>
       </c>
       <c r="L54" t="s">
-        <v>25</v>
-      </c>
-      <c r="M54" t="s">
-        <v>386</v>
+        <v>297</v>
       </c>
       <c r="N54" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15">
+        <v>389</v>
+      </c>
+      <c r="O54" t="s">
+        <v>390</v>
+      </c>
+      <c r="P54" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
       <c r="A55" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B55" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C55" t="s">
         <v>18</v>
@@ -4055,16 +4088,16 @@
         <v>20</v>
       </c>
       <c r="F55" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="G55" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="H55" t="s">
         <v>23</v>
       </c>
       <c r="I55" t="s">
-        <v>233</v>
+        <v>24</v>
       </c>
       <c r="J55" t="s">
         <v>23</v>
@@ -4076,39 +4109,39 @@
         <v>25</v>
       </c>
       <c r="M55" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="N55" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
       <c r="A56" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B56" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C56" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="E56" t="s">
         <v>20</v>
       </c>
       <c r="F56" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="G56" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="H56" t="s">
         <v>23</v>
       </c>
       <c r="I56" t="s">
-        <v>398</v>
+        <v>242</v>
       </c>
       <c r="J56" t="s">
         <v>23</v>
@@ -4117,80 +4150,80 @@
         <v>23</v>
       </c>
       <c r="L56" t="s">
+        <v>25</v>
+      </c>
+      <c r="M56" t="s">
+        <v>401</v>
+      </c>
+      <c r="N56" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57" t="s">
+        <v>403</v>
+      </c>
+      <c r="B57" t="s">
+        <v>404</v>
+      </c>
+      <c r="C57" t="s">
+        <v>84</v>
+      </c>
+      <c r="D57" t="s">
+        <v>85</v>
+      </c>
+      <c r="E57" t="s">
+        <v>20</v>
+      </c>
+      <c r="F57" t="s">
+        <v>405</v>
+      </c>
+      <c r="G57" t="s">
+        <v>406</v>
+      </c>
+      <c r="H57" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" t="s">
+        <v>407</v>
+      </c>
+      <c r="J57" t="s">
+        <v>23</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
         <v>65</v>
       </c>
-      <c r="M56" t="s">
-        <v>399</v>
-      </c>
-      <c r="N56" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15">
-      <c r="A57" t="s">
-        <v>401</v>
-      </c>
-      <c r="B57" t="s">
-        <v>402</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="M57" t="s">
+        <v>408</v>
+      </c>
+      <c r="N57" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58" t="s">
+        <v>410</v>
+      </c>
+      <c r="B58" t="s">
+        <v>411</v>
+      </c>
+      <c r="C58" t="s">
         <v>51</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D58" t="s">
         <v>52</v>
       </c>
-      <c r="E57" t="s">
+      <c r="E58" t="s">
         <v>43</v>
       </c>
-      <c r="F57" t="s">
-        <v>403</v>
-      </c>
-      <c r="G57" t="s">
-        <v>404</v>
-      </c>
-      <c r="H57" t="s">
-        <v>23</v>
-      </c>
-      <c r="I57" t="s">
-        <v>24</v>
-      </c>
-      <c r="J57" t="s">
-        <v>23</v>
-      </c>
-      <c r="K57" t="s">
-        <v>23</v>
-      </c>
-      <c r="L57" t="s">
-        <v>55</v>
-      </c>
-      <c r="M57" t="s">
-        <v>405</v>
-      </c>
-      <c r="N57" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15">
-      <c r="A58" t="s">
-        <v>407</v>
-      </c>
-      <c r="B58" t="s">
-        <v>408</v>
-      </c>
-      <c r="C58" t="s">
-        <v>18</v>
-      </c>
-      <c r="D58" t="s">
-        <v>19</v>
-      </c>
-      <c r="E58" t="s">
-        <v>20</v>
-      </c>
       <c r="F58" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="G58" t="s">
-        <v>72</v>
+        <v>413</v>
       </c>
       <c r="H58" t="s">
         <v>23</v>
@@ -4205,36 +4238,36 @@
         <v>23</v>
       </c>
       <c r="L58" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="M58" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="N58" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
       <c r="A59" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="B59" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="C59" t="s">
-        <v>352</v>
+        <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>353</v>
+        <v>19</v>
       </c>
       <c r="E59" t="s">
         <v>20</v>
       </c>
       <c r="F59" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="G59" t="s">
-        <v>354</v>
+        <v>72</v>
       </c>
       <c r="H59" t="s">
         <v>23</v>
@@ -4252,83 +4285,86 @@
         <v>65</v>
       </c>
       <c r="M59" t="s">
-        <v>53</v>
+        <v>419</v>
       </c>
       <c r="N59" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
       <c r="A60" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="B60" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="C60" t="s">
-        <v>115</v>
+        <v>361</v>
       </c>
       <c r="D60" t="s">
-        <v>108</v>
+        <v>362</v>
       </c>
       <c r="E60" t="s">
         <v>20</v>
       </c>
       <c r="F60" t="s">
+        <v>423</v>
+      </c>
+      <c r="G60" t="s">
+        <v>363</v>
+      </c>
+      <c r="H60" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" t="s">
+        <v>24</v>
+      </c>
+      <c r="J60" t="s">
+        <v>23</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>65</v>
+      </c>
+      <c r="M60" t="s">
+        <v>53</v>
+      </c>
+      <c r="N60" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61" t="s">
+        <v>425</v>
+      </c>
+      <c r="B61" t="s">
+        <v>426</v>
+      </c>
+      <c r="C61" t="s">
+        <v>115</v>
+      </c>
+      <c r="D61" t="s">
+        <v>108</v>
+      </c>
+      <c r="E61" t="s">
+        <v>20</v>
+      </c>
+      <c r="F61" t="s">
         <v>109</v>
       </c>
-      <c r="G60" t="s">
-        <v>418</v>
-      </c>
-      <c r="H60" t="s">
-        <v>23</v>
-      </c>
-      <c r="I60" t="s">
-        <v>23</v>
-      </c>
-      <c r="J60" t="s">
-        <v>23</v>
-      </c>
-      <c r="K60" t="s">
-        <v>23</v>
-      </c>
-      <c r="L60" t="s">
-        <v>25</v>
-      </c>
-      <c r="M60" t="s">
-        <v>419</v>
-      </c>
-      <c r="N60" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15">
-      <c r="A61" t="s">
-        <v>311</v>
-      </c>
-      <c r="B61" t="s">
-        <v>312</v>
-      </c>
-      <c r="C61" t="s">
-        <v>18</v>
-      </c>
-      <c r="D61" t="s">
-        <v>313</v>
-      </c>
-      <c r="E61" t="s">
-        <v>43</v>
-      </c>
       <c r="G61" t="s">
-        <v>314</v>
+        <v>427</v>
       </c>
       <c r="H61" t="s">
-        <v>179</v>
+        <v>23</v>
       </c>
       <c r="I61" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J61" t="s">
-        <v>187</v>
+        <v>23</v>
       </c>
       <c r="K61" t="s">
         <v>23</v>
@@ -4337,45 +4373,39 @@
         <v>25</v>
       </c>
       <c r="M61" t="s">
-        <v>188</v>
+        <v>428</v>
       </c>
       <c r="N61" t="s">
-        <v>420</v>
-      </c>
-      <c r="O61" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
       <c r="A62" t="s">
-        <v>421</v>
+        <v>320</v>
       </c>
       <c r="B62" t="s">
-        <v>422</v>
+        <v>321</v>
       </c>
       <c r="C62" t="s">
-        <v>137</v>
+        <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>138</v>
+        <v>322</v>
       </c>
       <c r="E62" t="s">
-        <v>20</v>
-      </c>
-      <c r="F62" t="s">
-        <v>423</v>
+        <v>43</v>
       </c>
       <c r="G62" t="s">
-        <v>424</v>
+        <v>323</v>
       </c>
       <c r="H62" t="s">
-        <v>23</v>
+        <v>179</v>
       </c>
       <c r="I62" t="s">
-        <v>425</v>
+        <v>24</v>
       </c>
       <c r="J62" t="s">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="K62" t="s">
         <v>23</v>
@@ -4384,53 +4414,100 @@
         <v>25</v>
       </c>
       <c r="M62" t="s">
-        <v>426</v>
+        <v>188</v>
       </c>
       <c r="N62" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15">
+        <v>429</v>
+      </c>
+      <c r="O62" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
       <c r="A63" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B63" t="s">
+        <v>431</v>
+      </c>
+      <c r="C63" t="s">
+        <v>137</v>
+      </c>
+      <c r="D63" t="s">
+        <v>138</v>
+      </c>
+      <c r="E63" t="s">
+        <v>20</v>
+      </c>
+      <c r="F63" t="s">
+        <v>432</v>
+      </c>
+      <c r="G63" t="s">
+        <v>433</v>
+      </c>
+      <c r="H63" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" t="s">
+        <v>434</v>
+      </c>
+      <c r="J63" t="s">
+        <v>23</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>25</v>
+      </c>
+      <c r="M63" t="s">
+        <v>435</v>
+      </c>
+      <c r="N63" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
+      <c r="A64" t="s">
+        <v>437</v>
+      </c>
+      <c r="B64" t="s">
         <v>151</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C64" t="s">
         <v>30</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D64" t="s">
         <v>31</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E64" t="s">
         <v>32</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F64" t="s">
         <v>152</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G64" t="s">
         <v>34</v>
       </c>
-      <c r="H63" t="s">
-        <v>23</v>
-      </c>
-      <c r="I63" t="s">
-        <v>23</v>
-      </c>
-      <c r="J63" t="s">
-        <v>23</v>
-      </c>
-      <c r="K63" t="s">
-        <v>23</v>
-      </c>
-      <c r="L63" t="s">
+      <c r="H64" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" t="s">
+        <v>23</v>
+      </c>
+      <c r="J64" t="s">
+        <v>23</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
         <v>153</v>
       </c>
-      <c r="M63" t="s">
+      <c r="M64" t="s">
         <v>154</v>
       </c>
-      <c r="N63" t="s">
+      <c r="N64" t="s">
         <v>112</v>
       </c>
     </row>
